--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1150,7 +1150,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1279,7 +1279,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -1348,7 +1348,7 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1468,7 +1468,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1539,7 +1539,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1908,7 +1908,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="69.35546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -9445,12 +9445,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO64">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="498">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -712,6 +712,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedInd, player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedTime</t>
   </si>
   <si>
@@ -728,6 +731,12 @@
 </t>
   </si>
   <si>
+    <t>Patient.deceased[x]:deceasedBoolean</t>
+  </si>
+  <si>
+    <t>deceasedBoolean</t>
+  </si>
+  <si>
     <t>Patient.address</t>
   </si>
   <si>
@@ -749,9 +758,6 @@
   <si>
     <t xml:space="preserve">value:use}
 </t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>addr</t>
@@ -1880,7 +1886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.03125" customWidth="true" bestFit="true"/>
@@ -4129,7 +4135,7 @@
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>214</v>
@@ -4147,7 +4153,7 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>173</v>
@@ -4156,7 +4162,7 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4164,13 +4170,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
@@ -4192,7 +4198,7 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>216</v>
@@ -4268,7 +4274,7 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>173</v>
@@ -4277,7 +4283,7 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4285,12 +4291,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>79</v>
       </c>
@@ -4305,25 +4313,25 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>166</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4360,23 +4368,25 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>79</v>
@@ -4385,16 +4395,16 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>235</v>
+        <v>173</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4402,14 +4412,12 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4430,19 +4438,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4479,19 +4487,17 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4506,16 +4512,16 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4526,9 +4532,11 @@
         <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4546,19 +4554,23 @@
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4606,31 +4618,31 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4638,21 +4650,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
@@ -4664,17 +4676,15 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4711,31 +4721,31 @@
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>173</v>
@@ -4755,16 +4765,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4783,15 +4791,17 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4828,19 +4838,19 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4855,7 +4865,7 @@
         <v>138</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>79</v>
@@ -4872,13 +4882,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>79</v>
@@ -4900,13 +4910,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4957,7 +4967,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4989,58 +4999,56 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>79</v>
@@ -5052,13 +5060,13 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -5076,22 +5084,22 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>79</v>
@@ -5100,7 +5108,7 @@
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5108,10 +5116,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5119,7 +5127,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>87</v>
@@ -5128,7 +5136,7 @@
         <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>88</v>
@@ -5137,27 +5145,29 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>79</v>
@@ -5172,10 +5182,10 @@
         <v>198</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5193,7 +5203,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5208,7 +5218,7 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>79</v>
@@ -5217,7 +5227,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5225,10 +5235,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5251,20 +5261,18 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5276,7 +5284,7 @@
         <v>79</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>79</v>
@@ -5288,13 +5296,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5312,7 +5320,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5327,7 +5335,7 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>79</v>
@@ -5336,7 +5344,7 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5344,10 +5352,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5358,7 +5366,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5370,16 +5378,20 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5391,7 +5403,7 @@
         <v>79</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>79</v>
@@ -5427,13 +5439,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5442,7 +5454,7 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>79</v>
@@ -5451,7 +5463,7 @@
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5459,21 +5471,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>303</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5485,13 +5497,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5506,7 +5518,7 @@
         <v>79</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>79</v>
@@ -5542,13 +5554,13 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
@@ -5557,7 +5569,7 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
@@ -5566,7 +5578,7 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5574,14 +5586,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5600,17 +5612,15 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5623,7 +5633,7 @@
         <v>79</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>79</v>
@@ -5659,7 +5669,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5674,7 +5684,7 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -5683,7 +5693,7 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5691,14 +5701,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5717,15 +5727,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5738,7 +5750,7 @@
         <v>79</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>79</v>
@@ -5774,7 +5786,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5789,7 +5801,7 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -5798,7 +5810,7 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5806,14 +5818,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5832,13 +5844,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5853,7 +5865,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5889,7 +5901,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5904,7 +5916,7 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
@@ -5913,7 +5925,7 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5921,14 +5933,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5947,17 +5959,15 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5970,7 +5980,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -6006,7 +6016,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6021,7 +6031,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
@@ -6030,7 +6040,7 @@
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6038,10 +6048,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6064,18 +6074,18 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>347</v>
+        <v>243</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6087,7 +6097,7 @@
         <v>79</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>79</v>
@@ -6123,7 +6133,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6138,7 +6148,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>79</v>
@@ -6147,7 +6157,7 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6155,10 +6165,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6178,20 +6188,20 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6204,7 +6214,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6216,13 +6226,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6240,7 +6250,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6255,16 +6265,16 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6272,10 +6282,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6298,19 +6308,17 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6335,13 +6343,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6359,7 +6367,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6374,16 +6382,16 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>173</v>
+        <v>366</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6391,10 +6399,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6405,7 +6413,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6417,19 +6425,19 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6478,13 +6486,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6493,7 +6501,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>173</v>
@@ -6502,7 +6510,7 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6510,10 +6518,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6536,19 +6544,19 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6597,7 +6605,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6609,10 +6617,10 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>388</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>173</v>
@@ -6621,7 +6629,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6629,10 +6637,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6643,7 +6651,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6655,16 +6663,20 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>242</v>
+        <v>386</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6712,25 +6724,25 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6744,21 +6756,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6770,17 +6782,15 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6829,19 +6839,19 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>173</v>
@@ -6861,14 +6871,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>393</v>
+        <v>146</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6881,26 +6891,24 @@
         <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>394</v>
+        <v>249</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6948,7 +6956,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>252</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6963,7 +6971,7 @@
         <v>138</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>79</v>
@@ -6980,14 +6988,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7000,23 +7008,25 @@
         <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>356</v>
+        <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7041,13 +7051,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7065,7 +7075,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7077,19 +7087,19 @@
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>403</v>
+        <v>130</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7097,10 +7107,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7111,7 +7121,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7123,17 +7133,17 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>176</v>
+        <v>358</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7158,13 +7168,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7182,13 +7192,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7197,7 +7207,7 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>181</v>
+        <v>405</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>173</v>
@@ -7206,7 +7216,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7214,10 +7224,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7228,7 +7238,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7240,19 +7250,17 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>189</v>
+        <v>410</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7301,13 +7309,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7316,7 +7324,7 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>173</v>
@@ -7325,7 +7333,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7333,10 +7341,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7347,7 +7355,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7359,17 +7367,19 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>418</v>
+        <v>189</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7418,13 +7428,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7433,7 +7443,7 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>173</v>
@@ -7442,7 +7452,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7450,10 +7460,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7476,17 +7486,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>194</v>
+        <v>418</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7511,13 +7521,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7535,7 +7545,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7550,7 +7560,7 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>173</v>
@@ -7559,7 +7569,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7567,10 +7577,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7593,17 +7603,17 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>425</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>426</v>
+        <v>194</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7628,13 +7638,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7652,7 +7662,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7661,13 +7671,13 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>430</v>
+        <v>201</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>173</v>
@@ -7676,7 +7686,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7684,10 +7694,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7710,16 +7720,18 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>347</v>
+        <v>427</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7767,7 +7779,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7776,13 +7788,13 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>173</v>
@@ -7791,7 +7803,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7799,10 +7811,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7813,7 +7825,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7825,20 +7837,16 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7886,13 +7894,13 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
@@ -7901,10 +7909,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>442</v>
+        <v>173</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7918,10 +7926,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7932,7 +7940,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7944,16 +7952,20 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>242</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8001,25 +8013,25 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>244</v>
+        <v>438</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>173</v>
+        <v>443</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8033,21 +8045,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8059,17 +8071,15 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8118,19 +8128,19 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>173</v>
@@ -8150,14 +8160,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>393</v>
+        <v>146</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8170,26 +8180,24 @@
         <v>79</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>249</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8237,7 +8245,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>396</v>
+        <v>252</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8252,7 +8260,7 @@
         <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>79</v>
@@ -8269,45 +8277,45 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>356</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>449</v>
+        <v>149</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8332,13 +8340,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8356,31 +8364,31 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>446</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>451</v>
+        <v>130</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>453</v>
+        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8388,10 +8396,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8399,7 +8407,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
@@ -8414,19 +8422,19 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>166</v>
+        <v>358</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8451,13 +8459,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8475,10 +8483,10 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>87</v>
@@ -8490,16 +8498,16 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8507,21 +8515,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8533,18 +8541,20 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>464</v>
+        <v>166</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8592,13 +8602,13 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
@@ -8607,16 +8617,16 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>173</v>
+        <v>462</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8624,21 +8634,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8647,23 +8657,21 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8711,13 +8719,13 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
@@ -8726,16 +8734,16 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>475</v>
+        <v>173</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>79</v>
+        <v>471</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8743,10 +8751,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8757,31 +8765,31 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -8830,13 +8838,13 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
@@ -8845,10 +8853,10 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>173</v>
+        <v>477</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -8862,10 +8870,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8876,28 +8884,32 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -8945,25 +8957,25 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>244</v>
+        <v>478</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8977,21 +8989,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9003,17 +9015,15 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9062,19 +9072,19 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>173</v>
@@ -9094,14 +9104,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>393</v>
+        <v>146</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9114,26 +9124,24 @@
         <v>79</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>249</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O62" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9181,7 +9189,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>396</v>
+        <v>252</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9196,7 +9204,7 @@
         <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>79</v>
@@ -9213,44 +9221,46 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>486</v>
+        <v>132</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>487</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>488</v>
+        <v>397</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9298,31 +9308,31 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>485</v>
+        <v>398</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>490</v>
+        <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9330,10 +9340,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9356,15 +9366,17 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>488</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9389,13 +9401,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>494</v>
+        <v>79</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9413,7 +9425,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>87</v>
@@ -9428,7 +9440,7 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>495</v>
+        <v>158</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>173</v>
@@ -9437,14 +9449,129 @@
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>79</v>
+        <v>492</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO64">
+  <autoFilter ref="A1:AO65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9454,7 +9581,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-skrs-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
